--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104742_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104742_W32.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3583</v>
+        <v>5.5012</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4058</v>
+        <v>3.4741</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9525</v>
+        <v>2.0271</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8767</v>
+        <v>3.8718</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1045</v>
+        <v>2.1024</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7722</v>
+        <v>1.7694</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2342</v>
+        <v>3.2225</v>
       </c>
       <c r="K2" t="n">
-        <v>1.233</v>
+        <v>1.2271</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0012</v>
+        <v>1.9955</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6425</v>
+        <v>0.6493</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8754</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.229</v>
+        <v>-0.226</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0037</v>
+        <v>1.1545</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3975</v>
+        <v>0.6873</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4012</v>
+        <v>0.4672</v>
       </c>
       <c r="V2" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0611</v>
+        <v>2.9835</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1625</v>
+        <v>0.5625</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8986</v>
+        <v>2.421</v>
       </c>
       <c r="G3" t="n">
-        <v>1.815</v>
+        <v>1.8032</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4667</v>
+        <v>2.4593</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6518</v>
+        <v>-0.656</v>
       </c>
       <c r="J3" t="n">
-        <v>1.951</v>
+        <v>1.9288</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3165</v>
+        <v>2.3023</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3655</v>
+        <v>-0.3735</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1361</v>
+        <v>-0.1255</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1502</v>
+        <v>0.157</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2863</v>
+        <v>-0.2826</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6328</v>
+        <v>1.5656</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4834</v>
+        <v>0.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1494</v>
+        <v>0.6556</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2684</v>
+        <v>1.8903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.803</v>
+        <v>0.5689</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4654</v>
+        <v>1.3214</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6022</v>
+        <v>2.5981</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0197</v>
+        <v>2.0139</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5825</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8058</v>
+        <v>2.7949</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4637</v>
+        <v>1.4544</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3421</v>
+        <v>1.3405</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2036</v>
+        <v>-0.1968</v>
       </c>
       <c r="N4" t="n">
-        <v>0.556</v>
+        <v>0.5595</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8018</v>
+        <v>1.432</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0415</v>
+        <v>0.8242</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7602</v>
+        <v>0.6077</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8111</v>
+        <v>1.6721</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6609</v>
+        <v>-0.7117</v>
       </c>
       <c r="F5" t="n">
-        <v>2.472</v>
+        <v>2.3839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7971</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2119</v>
+        <v>0.2124</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5855</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6079</v>
+        <v>-0.609</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7198</v>
+        <v>-0.7207</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M5" t="n">
-        <v>1.405</v>
+        <v>1.4069</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9317</v>
+        <v>0.9331</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4733</v>
+        <v>0.4738</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1049</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7195</v>
+        <v>0.6712</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3854</v>
+        <v>0.294</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1421</v>
+        <v>1.4437</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0344</v>
+        <v>0.2237</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1077</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7844</v>
+        <v>-1.784</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8641</v>
+        <v>-1.8618</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.9282</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0856</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8345</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8666</v>
+        <v>-0.8558</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1652</v>
+        <v>0.1715</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0319</v>
+        <v>-1.0273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0625</v>
+        <v>0.3659</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0944</v>
+        <v>0.1111</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1569</v>
+        <v>0.2548</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.785</v>
+        <v>1.2873</v>
       </c>
       <c r="E7" t="n">
-        <v>1.081</v>
+        <v>1.2211</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.296</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2237</v>
+        <v>-2.2233</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6379</v>
+        <v>-0.6401</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5858</v>
+        <v>-1.5832</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0958</v>
+        <v>-0.1069</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3448</v>
+        <v>-0.3522</v>
       </c>
       <c r="L7" t="n">
-        <v>0.249</v>
+        <v>0.2453</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1278</v>
+        <v>-2.1164</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8348</v>
+        <v>-1.8285</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2189</v>
+        <v>0.2845</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2332</v>
+        <v>-0.077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0144</v>
+        <v>0.3616</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4101</v>
+        <v>1.405</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2088</v>
+        <v>0.6455</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9089</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.443</v>
+        <v>-0.2633</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4678</v>
+        <v>1.4711</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4418</v>
+        <v>1.4442</v>
       </c>
       <c r="I8" t="n">
-        <v>0.026</v>
+        <v>0.0269</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0668</v>
+        <v>3.0557</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9911</v>
+        <v>0.9858</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0758</v>
+        <v>2.0699</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5991</v>
+        <v>-1.5846</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4507</v>
+        <v>0.4584</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0498</v>
+        <v>-2.043</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1231</v>
+        <v>0.3126</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>-0.0283</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1796</v>
+        <v>0.3408</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3796</v>
+        <v>-0.347</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.067</v>
+        <v>-0.0677</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3126</v>
+        <v>-0.2793</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1733</v>
+        <v>-0.1716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0045</v>
+        <v>0.0056</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1778</v>
+        <v>-0.1772</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0718</v>
+        <v>0.0717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2451</v>
+        <v>-0.2433</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4336</v>
+        <v>-0.403</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2947</v>
+        <v>-0.2636</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6114</v>
+        <v>-1.3094</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8978</v>
+        <v>1.7366</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2864</v>
+        <v>-3.0459</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.177</v>
+        <v>0.1365</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3802</v>
+        <v>0.9159</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7968</v>
+        <v>-0.7793</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9422</v>
+        <v>1.6834</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6506999999999999</v>
+        <v>1.7064</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2915</v>
+        <v>-0.023</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2348</v>
+        <v>-1.5469</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2705</v>
+        <v>-0.7906</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5052</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2937</v>
+        <v>-0.3368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0444</v>
+        <v>0.0531</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2493</v>
+        <v>-0.3899</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0913</v>
+        <v>-1.792</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0913</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1</v>
+        <v>-1.4871</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0872</v>
+        <v>-2.816</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1872</v>
+        <v>1.3289</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1368</v>
+        <v>1.0538</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9144</v>
+        <v>0.7007</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7776</v>
+        <v>0.3531</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6929</v>
+        <v>0.1062</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7108</v>
+        <v>0.0689</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.018</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5561</v>
+        <v>0.9476</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7965</v>
+        <v>0.6317</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7596000000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6816</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1221</v>
+        <v>0.8234</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>0.4923</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5164</v>
+        <v>0.3311</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7963</v>
+        <v>-0.8603</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7963</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1873</v>
+        <v>-1.9461</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3518</v>
+        <v>-1.9348</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1645</v>
+        <v>-0.0112</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0531</v>
+        <v>-3.177</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7002</v>
+        <v>-0.3792</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3528</v>
+        <v>-2.7978</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1064</v>
+        <v>-1.9485</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06909999999999999</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>-1.2967</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9467</v>
+        <v>-1.2285</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6311</v>
+        <v>0.2725</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3156</v>
+        <v>-1.5011</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4991</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4078</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1231</v>
+        <v>0.9546</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0504</v>
+        <v>0.0136</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1165</v>
+        <v>-4.3515</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2935</v>
+        <v>-1.6388</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.823</v>
+        <v>-2.7126</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3615</v>
+        <v>-3.3641</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5102</v>
+        <v>-0.5111</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.8514</v>
+        <v>-2.853</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1962</v>
+        <v>-2.2052</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.42</v>
+        <v>-0.4244</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7762</v>
+        <v>-1.7808</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1654</v>
+        <v>-1.1588</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0902</v>
+        <v>-0.0866</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9966</v>
+        <v>0.7559</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.5664</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0939</v>
+        <v>0.1895</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8875</v>
+        <v>-2.8814</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8875</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.239999999999998</v>
+        <v>5.9825</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04539999999999922</v>
+        <v>1.5268</v>
       </c>
       <c r="F14" t="n">
-        <v>4.285300000000001</v>
+        <v>4.456200000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0288</v>
+        <v>1.0124</v>
       </c>
       <c r="H14" t="n">
-        <v>8.415100000000001</v>
+        <v>8.4018</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.3866</v>
+        <v>-7.389200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>7.169000000000001</v>
+        <v>7.065400000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5979</v>
+        <v>5.536699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.571100000000001</v>
+        <v>1.528800000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.140400000000001</v>
+        <v>-6.0528</v>
       </c>
       <c r="N14" t="n">
-        <v>2.817000000000001</v>
+        <v>2.8651</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.957500000000001</v>
+        <v>-8.918000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.136</v>
+        <v>1.1383</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4953</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6311</v>
+        <v>13.658</v>
       </c>
       <c r="S14" t="n">
-        <v>6.1214</v>
+        <v>7.8744</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3689</v>
+        <v>4.0845</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7527</v>
+        <v>3.7898</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.0461</v>
+        <v>-4.042400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9122</v>
+        <v>2.8964</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.9583</v>
+        <v>-6.938800000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3556</v>
+        <v>7.0311</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1588</v>
+        <v>6.3019</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1968</v>
+        <v>0.7291</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3849</v>
+        <v>6.7602</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6567</v>
+        <v>-0.4342</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7282</v>
+        <v>7.1944</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8408</v>
+        <v>7.1419</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4614</v>
+        <v>0.1272</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3794</v>
+        <v>7.0148</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5441</v>
+        <v>-0.3817</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1953</v>
+        <v>-0.5613</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3488</v>
+        <v>0.1796</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0381</v>
+        <v>-1.8186</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3388</v>
+        <v>-1.1084</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3007</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4782</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1151</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.026</v>
+        <v>5.3599</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9774</v>
+        <v>3.8907</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0485</v>
+        <v>1.4692</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7632</v>
+        <v>3.386</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4381</v>
+        <v>0.655</v>
       </c>
       <c r="I16" t="n">
-        <v>7.2013</v>
+        <v>2.731</v>
       </c>
       <c r="J16" t="n">
-        <v>7.1612</v>
+        <v>1.8324</v>
       </c>
       <c r="K16" t="n">
-        <v>0.133</v>
+        <v>0.4547</v>
       </c>
       <c r="L16" t="n">
-        <v>7.0282</v>
+        <v>1.3778</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.398</v>
+        <v>1.5536</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5711000000000001</v>
+        <v>0.2003</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1731</v>
+        <v>1.3532</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8175</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.8285</v>
+        <v>1.0453</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4575</v>
+        <v>1.0889</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.371</v>
+        <v>-0.0436</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6369</v>
+        <v>0.4733</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6369</v>
+        <v>2.1075</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8409</v>
+        <v>0.846</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.351</v>
+        <v>-0.9042</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1919</v>
+        <v>1.7502</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7163</v>
+        <v>3.7186</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2487</v>
+        <v>-1.2466</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9651</v>
+        <v>4.9652</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5998</v>
+        <v>4.5873</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>5.4803</v>
+        <v>5.4738</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8835</v>
+        <v>-0.8687</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3682</v>
+        <v>-0.3601</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5153</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1806</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.7709</v>
+        <v>-4.7803</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4673</v>
+        <v>-0.4596</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1799</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7126</v>
+        <v>0.2515</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2964</v>
+        <v>0.8445</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4697</v>
+        <v>-1.1281</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7661</v>
+        <v>1.9726</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1198</v>
+        <v>1.1207</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1631</v>
+        <v>1.1656</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0433</v>
+        <v>-0.0449</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6379</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1406</v>
+        <v>1.1376</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5026</v>
+        <v>-0.5071</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4819</v>
+        <v>0.4901</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0225</v>
+        <v>0.028</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4594</v>
+        <v>0.4622</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4368</v>
+        <v>0.1092</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.3929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3077</v>
+        <v>0.5021</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1651</v>
+        <v>-0.5901</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6961000000000001</v>
+        <v>-0.6645</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8612</v>
+        <v>0.0745</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4321</v>
+        <v>-1.946</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9009</v>
+        <v>-0.9303</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5312</v>
+        <v>-1.0157</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4206</v>
+        <v>-0.9727</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4951</v>
+        <v>-0.1831</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>-0.7896</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0115</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4058</v>
+        <v>-0.7472</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6058</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4544</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7214</v>
+        <v>-0.0977</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0254</v>
+        <v>-0.0073</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6959</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0913</v>
+        <v>0.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0913</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8155</v>
+        <v>-0.8055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5343</v>
+        <v>-0.4644</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2812</v>
+        <v>-0.3411</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9473</v>
+        <v>-0.4908</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9294</v>
+        <v>-0.3881</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0179</v>
+        <v>-0.1027</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9669</v>
+        <v>0.1117</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.178</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7889</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9804</v>
+        <v>-0.6025</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7514</v>
+        <v>-0.3881</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.229</v>
+        <v>-0.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1359</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.323</v>
+        <v>-0.5424</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1138</v>
+        <v>-0.3485</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4368</v>
+        <v>-0.1939</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8391</v>
+        <v>-0.9162</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4624</v>
+        <v>0.2165</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3767</v>
+        <v>-1.1326</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4939</v>
+        <v>-2.4271</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3907</v>
+        <v>-0.8991</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1032</v>
+        <v>-1.528</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1118</v>
+        <v>-0.4221</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.4966</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1118</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6058</v>
+        <v>-2.005</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3907</v>
+        <v>-0.4025</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.215</v>
+        <v>-1.6025</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5724</v>
+        <v>-0.0338</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.347</v>
+        <v>-0.4509</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2253</v>
+        <v>0.4171</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9857</v>
+        <v>-1.2602</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-2.7033</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4287</v>
+        <v>1.4431</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7885</v>
+        <v>0.147</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1661</v>
+        <v>-0.0405</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.1875</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1406</v>
+        <v>-0.271</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0518</v>
+        <v>0.9513</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1924</v>
+        <v>-1.2223</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.648</v>
+        <v>0.4179</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2179</v>
+        <v>-0.9918</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4301</v>
+        <v>1.4097</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2272</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3332</v>
+        <v>0.0466</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4164</v>
+        <v>-0.156</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0833</v>
+        <v>0.2025</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1076</v>
+        <v>-1.6208</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2769</v>
+        <v>-0.3235</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1693</v>
+        <v>-1.2973</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1462</v>
+        <v>-0.7867</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0428</v>
+        <v>-0.164</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1891</v>
+        <v>-0.6227</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2605</v>
+        <v>-0.1421</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9565</v>
+        <v>0.0517</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.217</v>
+        <v>-0.1939</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4067</v>
+        <v>-0.6446</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9994</v>
+        <v>-0.2157</v>
       </c>
       <c r="O23" t="n">
-        <v>1.406</v>
+        <v>-0.4289</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7991</v>
+        <v>0.0278</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.1813</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0546</v>
+        <v>0.2091</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2246</v>
+        <v>-2.1895</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5019</v>
+        <v>-1.5052</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7227</v>
+        <v>-0.6843</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9485</v>
+        <v>-0.946</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1145</v>
+        <v>-0.113</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1596</v>
+        <v>-0.1563</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0451</v>
+        <v>-0.0433</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1145</v>
+        <v>-0.113</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1845</v>
+        <v>-1.1556</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4858</v>
+        <v>-0.4879</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6987</v>
+        <v>-0.6677</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.26</v>
+        <v>-4.3698</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.386</v>
+        <v>-4.0107</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8739</v>
+        <v>-0.3591</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.2098</v>
+        <v>-4.3383</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7679</v>
+        <v>-3.5177</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4419</v>
+        <v>-0.8205</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.6226</v>
+        <v>-3.0218</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.0015</v>
+        <v>-2.2245</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.6211</v>
+        <v>-0.7973</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5872</v>
+        <v>-1.3164</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7664</v>
+        <v>-1.2932</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8208</v>
+        <v>-0.0232</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9087</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9087</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7996</v>
+        <v>-1.1406</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7635</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0361</v>
+        <v>-0.6361</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1594</v>
+        <v>1.792</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.3612</v>
+        <v>-4.9904</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.5784</v>
+        <v>-3.1612</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7827</v>
+        <v>-1.8291</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.3391</v>
+        <v>-5.21</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.5163</v>
+        <v>-1.7689</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8228</v>
+        <v>-3.4411</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.0113</v>
+        <v>-2.6314</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.2164</v>
+        <v>-1.0072</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-1.6242</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3278</v>
+        <v>-2.5786</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2999</v>
+        <v>-0.7617</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0279</v>
+        <v>-1.8169</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1368</v>
+        <v>-0.5331</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0915</v>
+        <v>-0.5298</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0452</v>
+        <v>-0.0033</v>
       </c>
       <c r="V26" t="n">
-        <v>1.7963</v>
+        <v>-0.1578</v>
       </c>
       <c r="W26" t="n">
-        <v>1.7963</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.2399</v>
+        <v>-2.661</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.285299999999999</v>
+        <v>-4.456000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04550000000000032</v>
+        <v>1.7952</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.028800000000001</v>
+        <v>-1.0124</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.415100000000001</v>
+        <v>-8.4018</v>
       </c>
       <c r="I27" t="n">
-        <v>7.386399999999999</v>
+        <v>7.3895</v>
       </c>
       <c r="J27" t="n">
-        <v>6.1401</v>
+        <v>6.0531</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.8171</v>
+        <v>-2.8651</v>
       </c>
       <c r="L27" t="n">
-        <v>8.9574</v>
+        <v>8.918200000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.169099999999999</v>
+        <v>-7.0655</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.598100000000001</v>
+        <v>-5.5366</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.5711</v>
+        <v>-1.5288</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.135899999999999</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q27" t="n">
-        <v>-13.6312</v>
+        <v>-13.6579</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4952</v>
+        <v>12.5199</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.1217</v>
+        <v>-4.5525</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.7526</v>
+        <v>-3.7898</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.3689</v>
+        <v>-0.7628999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>4.046200000000001</v>
+        <v>4.0423</v>
       </c>
       <c r="W27" t="n">
-        <v>6.958399999999999</v>
+        <v>6.938699999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.912199999999999</v>
+        <v>-2.8964</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104742_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104742_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.938800000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104742_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-2.8964</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
